--- a/DataTables/DetailText/剧情/000_02书商来访.xlsx
+++ b/DataTables/DetailText/剧情/000_02书商来访.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40222900-1551-4944-93A9-37B6BB0CB666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0795A5-DB22-49F7-B288-9D094882F474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -198,10 +198,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>再者您这大作洋洋洒洒几百万字，还有大量插图。</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>虽然您这书确实是好书，可我们也不能做亏本买卖不是。</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -247,6 +243,10 @@
   </si>
   <si>
     <t>您的书确实是医家至宝，可当今世人爱看的是英雄演义，才子佳人，就算发行了恐怕也是卖不出去的。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>再者，您这大作洋洋洒洒几百万字，还有大量插图。</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -785,7 +785,7 @@
     </row>
     <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A2" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>32</v>
@@ -802,7 +802,7 @@
       <c r="H2" s="23"/>
       <c r="I2" s="22"/>
       <c r="J2" s="25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K2" s="23"/>
       <c r="L2" s="23" t="s">
@@ -1096,7 +1096,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1118,7 +1118,7 @@
         <v>11</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I2" s="31"/>
     </row>
@@ -1179,7 +1179,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I5" s="31"/>
     </row>
@@ -1223,7 +1223,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I7" s="32"/>
     </row>
@@ -1244,7 +1244,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I8" s="32"/>
     </row>
@@ -1265,7 +1265,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="29" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="I9" s="32"/>
     </row>
@@ -1286,7 +1286,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I10" s="32"/>
     </row>
@@ -1307,7 +1307,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I11" s="32"/>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I12" s="32"/>
     </row>
@@ -1351,7 +1351,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I13" s="32"/>
     </row>
@@ -1372,7 +1372,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I14" s="32"/>
     </row>
